--- a/input/attachments/ig-assets/xSHARE_Data_Elements_w_C-Codes_and_SNOMED_Codes.xlsx
+++ b/input/attachments/ig-assets/xSHARE_Data_Elements_w_C-Codes_and_SNOMED_Codes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk.sharepoint.com/sites/xSHARE/Shared Documents/WP5 European EHRxF in Clinical Research -  Core Set, and IPS-R/Task 5.3/01_xShare Core Harmonized Data Elements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/rbaker_cdisc_org/Documents/1 Real World Data - RWD/1_XSHARE/Spreadsheets for project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="547" documentId="8_{1986939B-D7B5-4382-A5AC-CF91999B4486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FD35DC4-DE82-4F28-8962-1FC63A1626F1}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{64D10A00-C890-4DEA-9F1F-3E1026052BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3855ABDC-26C3-4670-A728-967AD393EFBF}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-1440" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{95223DB1-F850-4F71-A8C9-AFEC72865D4B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{95223DB1-F850-4F71-A8C9-AFEC72865D4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Change History" sheetId="10" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="933">
   <si>
     <t>This is the Change History for the xSHARE IPS+ Data Elements Tab in this spreadsheet.</t>
   </si>
@@ -92,6 +92,9 @@
 Added Vital Sign Position of Person (VSPOS) data element</t>
   </si>
   <si>
+    <t>Added SUBJID C-Code</t>
+  </si>
+  <si>
     <t>This is the README for the xSHARE IPS+ Data Elements Tab in this spreadsheet.</t>
   </si>
   <si>
@@ -265,6 +268,9 @@
   </si>
   <si>
     <t>Research Subject Identifier for the study</t>
+  </si>
+  <si>
+    <t>C83083</t>
   </si>
   <si>
     <t>No code</t>
@@ -3025,7 +3031,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3140,13 +3146,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -3868,9 +3867,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3885,7 +3881,7 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3903,7 +3899,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3919,6 +3915,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3969,19 +3968,19 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4325,11 +4324,11 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W151"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="72"/>
     <col min="2" max="2" width="36.5703125" style="72" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.28515625" customWidth="1"/>
     <col min="5" max="5" width="64" style="77" customWidth="1"/>
   </cols>
@@ -4337,7 +4336,7 @@
     <row r="1" spans="2:23" s="72" customFormat="1">
       <c r="E1" s="75"/>
     </row>
-    <row r="2" spans="2:23" ht="18.75">
+    <row r="2" spans="2:23" ht="18">
       <c r="B2" s="118" t="s">
         <v>0</v>
       </c>
@@ -4409,16 +4408,16 @@
       <c r="W4" s="72"/>
     </row>
     <row r="5" spans="2:23">
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="104" t="s">
+      <c r="E5" s="103" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="72"/>
@@ -4441,10 +4440,10 @@
       <c r="W5" s="72"/>
     </row>
     <row r="6" spans="2:23">
-      <c r="B6" s="102">
+      <c r="B6" s="101">
         <v>1</v>
       </c>
-      <c r="C6" s="101">
+      <c r="C6" s="100">
         <v>45444</v>
       </c>
       <c r="D6" s="11" t="s">
@@ -4472,17 +4471,17 @@
       <c r="V6" s="72"/>
       <c r="W6" s="72"/>
     </row>
-    <row r="7" spans="2:23" ht="60">
+    <row r="7" spans="2:23" ht="57.6">
       <c r="B7" s="78">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="101">
+      <c r="C7" s="100">
         <v>45474</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="111" t="s">
+      <c r="E7" s="110" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="72"/>
@@ -4508,7 +4507,7 @@
       <c r="B8" s="78">
         <v>1.2</v>
       </c>
-      <c r="C8" s="101">
+      <c r="C8" s="100">
         <v>45533</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -4540,7 +4539,7 @@
       <c r="B9" s="78">
         <v>1.2</v>
       </c>
-      <c r="C9" s="101">
+      <c r="C9" s="100">
         <v>45569</v>
       </c>
       <c r="D9" s="11" t="s">
@@ -4568,11 +4567,11 @@
       <c r="V9" s="72"/>
       <c r="W9" s="72"/>
     </row>
-    <row r="10" spans="2:23" ht="45">
+    <row r="10" spans="2:23" ht="43.15">
       <c r="B10" s="78">
         <v>1.3</v>
       </c>
-      <c r="C10" s="101">
+      <c r="C10" s="100">
         <v>45623</v>
       </c>
       <c r="D10" s="11" t="s">
@@ -4601,10 +4600,18 @@
       <c r="W10" s="72"/>
     </row>
     <row r="11" spans="2:23">
-      <c r="B11" s="78"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="79"/>
+      <c r="B11" s="78">
+        <v>1.4</v>
+      </c>
+      <c r="C11" s="100">
+        <v>45966</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="79" t="s">
+        <v>12</v>
+      </c>
       <c r="F11" s="72"/>
       <c r="G11" s="72"/>
       <c r="H11" s="72"/>
@@ -4626,79 +4633,79 @@
     </row>
     <row r="12" spans="2:23" s="72" customFormat="1" ht="18" customHeight="1">
       <c r="B12" s="78"/>
-      <c r="C12" s="101"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="78"/>
       <c r="E12" s="79"/>
     </row>
     <row r="13" spans="2:23" s="72" customFormat="1">
       <c r="B13" s="78"/>
-      <c r="C13" s="101"/>
+      <c r="C13" s="100"/>
       <c r="D13" s="78"/>
       <c r="E13" s="79"/>
     </row>
     <row r="14" spans="2:23" s="72" customFormat="1">
       <c r="B14" s="78"/>
-      <c r="C14" s="101"/>
+      <c r="C14" s="100"/>
       <c r="D14" s="78"/>
       <c r="E14" s="79"/>
     </row>
     <row r="15" spans="2:23" s="72" customFormat="1">
       <c r="B15" s="78"/>
-      <c r="C15" s="101"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="78"/>
       <c r="E15" s="79"/>
     </row>
     <row r="16" spans="2:23" s="72" customFormat="1">
       <c r="B16" s="78"/>
-      <c r="C16" s="101"/>
+      <c r="C16" s="100"/>
       <c r="D16" s="78"/>
       <c r="E16" s="79"/>
     </row>
     <row r="17" spans="2:5" s="72" customFormat="1">
       <c r="B17" s="78"/>
-      <c r="C17" s="101"/>
+      <c r="C17" s="100"/>
       <c r="D17" s="78"/>
       <c r="E17" s="79"/>
     </row>
     <row r="18" spans="2:5" s="72" customFormat="1">
       <c r="B18" s="78"/>
-      <c r="C18" s="101"/>
+      <c r="C18" s="100"/>
       <c r="D18" s="78"/>
       <c r="E18" s="79"/>
     </row>
     <row r="19" spans="2:5" s="72" customFormat="1">
       <c r="B19" s="78"/>
-      <c r="C19" s="101"/>
+      <c r="C19" s="100"/>
       <c r="D19" s="78"/>
       <c r="E19" s="79"/>
     </row>
     <row r="20" spans="2:5" s="72" customFormat="1">
       <c r="B20" s="78"/>
-      <c r="C20" s="101"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="78"/>
       <c r="E20" s="79"/>
     </row>
     <row r="21" spans="2:5" s="72" customFormat="1">
       <c r="B21" s="78"/>
-      <c r="C21" s="101"/>
+      <c r="C21" s="100"/>
       <c r="D21" s="78"/>
       <c r="E21" s="79"/>
     </row>
     <row r="22" spans="2:5" s="72" customFormat="1">
       <c r="B22" s="78"/>
-      <c r="C22" s="101"/>
+      <c r="C22" s="100"/>
       <c r="D22" s="78"/>
       <c r="E22" s="79"/>
     </row>
     <row r="23" spans="2:5" s="72" customFormat="1">
       <c r="B23" s="78"/>
-      <c r="C23" s="101"/>
+      <c r="C23" s="100"/>
       <c r="D23" s="78"/>
       <c r="E23" s="79"/>
     </row>
     <row r="24" spans="2:5" s="72" customFormat="1">
       <c r="B24" s="78"/>
-      <c r="C24" s="101"/>
+      <c r="C24" s="100"/>
       <c r="D24" s="78"/>
       <c r="E24" s="79"/>
     </row>
@@ -5098,7 +5105,7 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:V178"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="72"/>
     <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
@@ -5109,9 +5116,9 @@
     <row r="1" spans="1:22" s="72" customFormat="1">
       <c r="D1" s="75"/>
     </row>
-    <row r="2" spans="1:22" ht="18.75">
+    <row r="2" spans="1:22" ht="18">
       <c r="B2" s="118" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="118"/>
       <c r="D2" s="118"/>
@@ -5136,7 +5143,7 @@
     </row>
     <row r="3" spans="1:22">
       <c r="B3" s="117" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="117"/>
       <c r="D3" s="117"/>
@@ -5207,10 +5214,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="B6" s="70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="76" t="s">
         <v>4</v>
@@ -5234,16 +5241,16 @@
       <c r="U6" s="72"/>
       <c r="V6" s="72"/>
     </row>
-    <row r="7" spans="1:22" s="69" customFormat="1" ht="30">
+    <row r="7" spans="1:22" s="69" customFormat="1" ht="28.9">
       <c r="A7" s="73"/>
       <c r="B7" s="81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="73"/>
       <c r="F7" s="73"/>
@@ -5264,16 +5271,16 @@
       <c r="U7" s="73"/>
       <c r="V7" s="73"/>
     </row>
-    <row r="8" spans="1:22" s="69" customFormat="1" ht="30">
+    <row r="8" spans="1:22" s="69" customFormat="1" ht="28.9">
       <c r="A8" s="73"/>
       <c r="B8" s="81" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="73"/>
       <c r="F8" s="73"/>
@@ -5294,16 +5301,16 @@
       <c r="U8" s="73"/>
       <c r="V8" s="73"/>
     </row>
-    <row r="9" spans="1:22" s="69" customFormat="1" ht="15.75">
+    <row r="9" spans="1:22" s="69" customFormat="1" ht="15.6">
       <c r="A9" s="73"/>
       <c r="B9" s="81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="73"/>
       <c r="F9" s="73"/>
@@ -5324,16 +5331,16 @@
       <c r="U9" s="73"/>
       <c r="V9" s="73"/>
     </row>
-    <row r="10" spans="1:22" s="69" customFormat="1" ht="60">
+    <row r="10" spans="1:22" s="69" customFormat="1" ht="57.6">
       <c r="A10" s="73"/>
       <c r="B10" s="81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" s="73"/>
       <c r="F10" s="73"/>
@@ -5354,16 +5361,16 @@
       <c r="U10" s="73"/>
       <c r="V10" s="73"/>
     </row>
-    <row r="11" spans="1:22" s="69" customFormat="1" ht="15.75">
+    <row r="11" spans="1:22" s="69" customFormat="1" ht="15.6">
       <c r="A11" s="73"/>
       <c r="B11" s="81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="71" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="74" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="73"/>
       <c r="F11" s="73"/>
@@ -5384,16 +5391,16 @@
       <c r="U11" s="73"/>
       <c r="V11" s="73"/>
     </row>
-    <row r="12" spans="1:22" s="69" customFormat="1" ht="75">
+    <row r="12" spans="1:22" s="69" customFormat="1" ht="72">
       <c r="A12" s="73"/>
       <c r="B12" s="81" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" s="73"/>
       <c r="F12" s="73"/>
@@ -5414,16 +5421,16 @@
       <c r="U12" s="73"/>
       <c r="V12" s="73"/>
     </row>
-    <row r="13" spans="1:22" s="69" customFormat="1" ht="15.75">
+    <row r="13" spans="1:22" s="69" customFormat="1" ht="15.6">
       <c r="A13" s="73"/>
       <c r="B13" s="81" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="73"/>
       <c r="F13" s="73"/>
@@ -5444,16 +5451,16 @@
       <c r="U13" s="73"/>
       <c r="V13" s="73"/>
     </row>
-    <row r="14" spans="1:22" s="69" customFormat="1" ht="15.75">
+    <row r="14" spans="1:22" s="69" customFormat="1" ht="15.6">
       <c r="A14" s="73"/>
       <c r="B14" s="81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="74" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="73"/>
       <c r="F14" s="73"/>
@@ -5474,16 +5481,16 @@
       <c r="U14" s="73"/>
       <c r="V14" s="73"/>
     </row>
-    <row r="15" spans="1:22" s="69" customFormat="1" ht="45">
+    <row r="15" spans="1:22" s="69" customFormat="1" ht="28.9">
       <c r="A15" s="73"/>
       <c r="B15" s="81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="74" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="73"/>
       <c r="F15" s="73"/>
@@ -5504,16 +5511,16 @@
       <c r="U15" s="73"/>
       <c r="V15" s="73"/>
     </row>
-    <row r="16" spans="1:22" s="69" customFormat="1" ht="15.75">
+    <row r="16" spans="1:22" s="69" customFormat="1" ht="15.6">
       <c r="A16" s="73"/>
       <c r="B16" s="81" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" s="73"/>
       <c r="F16" s="73"/>
@@ -5534,16 +5541,16 @@
       <c r="U16" s="73"/>
       <c r="V16" s="73"/>
     </row>
-    <row r="17" spans="1:22" s="69" customFormat="1" ht="15.75">
+    <row r="17" spans="1:22" s="69" customFormat="1" ht="15.6">
       <c r="A17" s="73"/>
       <c r="B17" s="81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="71" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="74" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="73"/>
       <c r="F17" s="73"/>
@@ -5564,16 +5571,16 @@
       <c r="U17" s="73"/>
       <c r="V17" s="73"/>
     </row>
-    <row r="18" spans="1:22" s="69" customFormat="1" ht="76.5">
+    <row r="18" spans="1:22" s="69" customFormat="1" ht="79.150000000000006">
       <c r="A18" s="73"/>
       <c r="B18" s="81" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="71" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="73"/>
       <c r="F18" s="73"/>
@@ -5597,13 +5604,13 @@
     <row r="19" spans="1:22" s="69" customFormat="1" ht="80.25" customHeight="1">
       <c r="A19" s="73"/>
       <c r="B19" s="81" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="71" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" s="73"/>
       <c r="F19" s="73"/>
@@ -5626,7 +5633,7 @@
     </row>
     <row r="20" spans="1:22">
       <c r="B20" s="119" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="120"/>
       <c r="D20" s="121"/>
@@ -5651,7 +5658,7 @@
     </row>
     <row r="21" spans="1:22">
       <c r="B21" s="122" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C21" s="122"/>
       <c r="D21" s="122"/>
@@ -5676,7 +5683,7 @@
     </row>
     <row r="22" spans="1:22">
       <c r="B22" s="123" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="124"/>
       <c r="D22" s="125"/>
@@ -5701,7 +5708,7 @@
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="126" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="127"/>
       <c r="D23" s="128"/>
@@ -5726,7 +5733,7 @@
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="78"/>
       <c r="D24" s="79"/>
@@ -5751,7 +5758,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="78"/>
       <c r="D25" s="79"/>
@@ -5776,7 +5783,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="78"/>
       <c r="D26" s="79"/>
@@ -5801,7 +5808,7 @@
     </row>
     <row r="27" spans="1:22" ht="35.25" customHeight="1">
       <c r="B27" s="123" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="124"/>
       <c r="D27" s="125"/>
@@ -6267,7 +6274,7 @@
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="39.140625" customWidth="1"/>
-    <col min="6" max="6" width="63.42578125" style="105" customWidth="1"/>
+    <col min="6" max="6" width="63.42578125" style="104" customWidth="1"/>
     <col min="7" max="7" width="39.140625" customWidth="1"/>
     <col min="8" max="8" width="23.140625" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
@@ -6279,577 +6286,579 @@
     <col min="16" max="16" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="31.5">
+    <row r="1" spans="1:14" ht="31.15">
       <c r="A1" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M1" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N1" s="53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="60">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="43.15">
       <c r="A2" s="39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="105" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" s="56"/>
+      <c r="N2" s="114"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.6">
+      <c r="A3" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="106" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H2" s="13" t="s">
+      <c r="C3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="56"/>
-      <c r="N2" s="115"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="82" t="s">
-        <v>68</v>
-      </c>
       <c r="F3" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>75</v>
-      </c>
       <c r="J3" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L3" s="55" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="25"/>
     </row>
-    <row r="4" spans="1:14" ht="105">
+    <row r="4" spans="1:14" ht="100.9">
       <c r="A4" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="107" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="F4" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L4" s="55" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M4" s="11"/>
       <c r="N4" s="27"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" ht="15.6">
       <c r="A5" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="107" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="F5" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" ht="31.5">
+    <row r="6" spans="1:14" ht="31.15">
       <c r="A6" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>96</v>
-      </c>
       <c r="J6" s="14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L6" s="55" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" spans="1:14" ht="30">
+    <row r="7" spans="1:14" ht="28.9">
       <c r="A7" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="M7" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.9">
+      <c r="A8" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="82" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="L7" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="M7" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="45">
-      <c r="A8" s="35" t="s">
-        <v>65</v>
-      </c>
       <c r="B8" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E8" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F8" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>110</v>
-      </c>
       <c r="J8" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L8" s="55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" ht="31.5">
+    <row r="9" spans="1:14" ht="31.15">
       <c r="A9" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="82" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L9" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="M9" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="57.6">
+      <c r="A10" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="82" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="82" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="L9" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="M9" s="63" t="s">
-        <v>126</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="75">
-      <c r="A10" s="35" t="s">
-        <v>65</v>
-      </c>
       <c r="B10" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E10" s="82" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F10" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>127</v>
-      </c>
       <c r="J10" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L10" s="55" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" spans="1:14" ht="60">
+    <row r="11" spans="1:14" ht="57.6">
       <c r="A11" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E11" s="82" t="s">
-        <v>136</v>
-      </c>
-      <c r="F11" s="107" t="s">
-        <v>68</v>
+        <v>138</v>
+      </c>
+      <c r="F11" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L11" s="55" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
     </row>
-    <row r="12" spans="1:14" ht="45">
+    <row r="12" spans="1:14" ht="43.15">
       <c r="A12" s="36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="84" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="84" t="s">
+        <v>148</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="L12" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="M12" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="N12" s="64" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="57.6">
+      <c r="A13" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="84" t="s">
-        <v>145</v>
-      </c>
-      <c r="F12" s="84" t="s">
-        <v>146</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="K12" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="L12" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="M12" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="N12" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="75">
-      <c r="A13" s="39" t="s">
-        <v>65</v>
-      </c>
       <c r="B13" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" s="83" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="83" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="L13" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="M13" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="N13" s="65" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.9">
+      <c r="A14" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="E13" s="83" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="83" t="s">
-        <v>157</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="L13" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="M13" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="N13" s="65" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="45">
-      <c r="A14" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>153</v>
-      </c>
       <c r="C14" s="18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E14" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="107" t="s">
-        <v>68</v>
+        <v>114</v>
+      </c>
+      <c r="F14" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I14" s="29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J14" s="29" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L14" s="58" t="s">
         <v>2</v>
@@ -6857,1523 +6866,1523 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" spans="1:14" ht="31.5">
+    <row r="15" spans="1:14" ht="31.15">
       <c r="A15" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E15" s="85" t="s">
-        <v>172</v>
-      </c>
-      <c r="F15" s="107" t="s">
-        <v>68</v>
+        <v>174</v>
+      </c>
+      <c r="F15" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L15" s="55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
     </row>
-    <row r="16" spans="1:14" ht="31.5">
+    <row r="16" spans="1:14" ht="31.15">
       <c r="A16" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E16" s="85" t="s">
-        <v>172</v>
-      </c>
-      <c r="F16" s="107" t="s">
-        <v>68</v>
+        <v>174</v>
+      </c>
+      <c r="F16" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K16" s="26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L16" s="59" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" spans="1:14" ht="31.5">
+    <row r="17" spans="1:14" ht="31.15">
       <c r="A17" s="30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E17" s="83" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F17" s="83" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L17" s="56" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M17" s="56"/>
       <c r="N17" s="56"/>
     </row>
-    <row r="18" spans="1:14" ht="45">
+    <row r="18" spans="1:14" ht="43.15">
       <c r="A18" s="47" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E18" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="107" t="s">
-        <v>68</v>
+        <v>114</v>
+      </c>
+      <c r="F18" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H18" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="I18" s="28" t="s">
-        <v>196</v>
-      </c>
       <c r="J18" s="28" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L18" s="58" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:14" ht="45">
+    <row r="19" spans="1:14" ht="43.15">
       <c r="A19" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D19" s="43" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E19" s="82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F19" s="106" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="I19" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="F19" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>201</v>
-      </c>
       <c r="J19" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L19" s="55" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
     </row>
-    <row r="20" spans="1:14" ht="45">
+    <row r="20" spans="1:14" ht="43.15">
       <c r="A20" s="21" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E20" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="107" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="F20" s="106" t="s">
+        <v>70</v>
       </c>
       <c r="G20" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="I20" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>209</v>
-      </c>
       <c r="J20" s="23" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L20" s="57" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
     </row>
-    <row r="21" spans="1:14" ht="60">
+    <row r="21" spans="1:14" ht="43.15">
       <c r="A21" s="16" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E21" s="83" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F21" s="83" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J21" s="19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L21" s="60" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M21" s="60"/>
       <c r="N21" s="60"/>
     </row>
-    <row r="22" spans="1:14" ht="45">
+    <row r="22" spans="1:14" ht="43.15">
       <c r="A22" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E22" s="82" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F22" s="82" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L22" s="55" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" spans="1:14" ht="45">
+    <row r="23" spans="1:14" ht="28.9">
       <c r="A23" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F23" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L23" s="55" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
     </row>
-    <row r="24" spans="1:14" ht="45">
+    <row r="24" spans="1:14" ht="43.15">
       <c r="A24" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E24" s="82" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L24" s="55" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M24" s="43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N24" s="64" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="90">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="86.45">
       <c r="A25" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E25" s="82" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F25" s="82" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L25" s="55" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" ht="43.5" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E26" s="82" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F26" s="82" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L26" s="55" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M26" s="43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N26" s="64" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="45">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.9">
       <c r="A27" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E27" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F27" s="82" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L27" s="55" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M27" s="43" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N27" s="64" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="45">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.9">
       <c r="A28" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E28" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F28" s="82" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L28" s="55" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M28" s="43" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N28" s="64" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="60">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="57.6">
       <c r="A29" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E29" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F29" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L29" s="55" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
     </row>
-    <row r="30" spans="1:14" ht="45">
+    <row r="30" spans="1:14" ht="43.15">
       <c r="A30" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E30" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F30" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L30" s="55" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
     </row>
-    <row r="31" spans="1:14" ht="75">
+    <row r="31" spans="1:14" ht="57.6">
       <c r="A31" s="24" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B31" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="D31" s="66" t="s">
+        <v>310</v>
+      </c>
+      <c r="E31" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="K31" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="L31" s="59" t="s">
         <v>217</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="D31" s="66" t="s">
-        <v>308</v>
-      </c>
-      <c r="E31" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="I31" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="J31" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="K31" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="L31" s="59" t="s">
-        <v>215</v>
       </c>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" ht="41.25" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D32" s="67" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E32" s="83" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F32" s="83" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G32" s="50" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L32" s="60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M32" s="60"/>
       <c r="N32" s="60"/>
     </row>
-    <row r="33" spans="1:14" ht="60">
+    <row r="33" spans="1:14" ht="43.15">
       <c r="A33" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D33" s="43" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E33" s="82" t="s">
+        <v>329</v>
+      </c>
+      <c r="F33" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="I33" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="F33" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>325</v>
-      </c>
       <c r="J33" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L33" s="55" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
     </row>
-    <row r="34" spans="1:14" ht="75">
+    <row r="34" spans="1:14" ht="72">
       <c r="A34" s="24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E34" s="82" t="s">
+        <v>337</v>
+      </c>
+      <c r="F34" s="82" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="H34" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="I34" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="F34" s="82" t="s">
-        <v>68</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="H34" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>333</v>
-      </c>
       <c r="J34" s="26" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L34" s="55" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
     </row>
-    <row r="35" spans="1:14" ht="30">
+    <row r="35" spans="1:14" ht="28.9">
       <c r="A35" s="24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E35" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F35" s="82" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H35" s="26" t="s">
+        <v>345</v>
+      </c>
+      <c r="I35" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="K35" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="L35" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="M35" s="43" t="s">
         <v>343</v>
       </c>
-      <c r="I35" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="J35" s="26" t="s">
-        <v>345</v>
-      </c>
-      <c r="K35" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="L35" s="55" t="s">
-        <v>347</v>
-      </c>
-      <c r="M35" s="43" t="s">
-        <v>341</v>
-      </c>
       <c r="N35" s="64" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="30">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.9">
       <c r="A36" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E36" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F36" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L36" s="55" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M36" s="11"/>
       <c r="N36" s="11"/>
     </row>
-    <row r="37" spans="1:14" ht="45">
+    <row r="37" spans="1:14" ht="28.9">
       <c r="A37" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D37" s="43" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E37" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F37" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H37" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="I37" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="I37" s="14" t="s">
-        <v>356</v>
-      </c>
       <c r="J37" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L37" s="59" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" spans="1:14" ht="45">
+    <row r="38" spans="1:14" ht="43.15">
       <c r="A38" s="51" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C38" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="E38" s="86" t="s">
+        <v>368</v>
+      </c>
+      <c r="F38" s="86" t="s">
+        <v>369</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>370</v>
+      </c>
+      <c r="H38" s="50" t="s">
+        <v>371</v>
+      </c>
+      <c r="I38" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="J38" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="K38" s="50" t="s">
+        <v>374</v>
+      </c>
+      <c r="L38" s="60" t="s">
+        <v>375</v>
+      </c>
+      <c r="M38" s="112" t="s">
+        <v>376</v>
+      </c>
+      <c r="N38" s="60" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.15">
+      <c r="A39" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="B39" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="E38" s="86" t="s">
-        <v>366</v>
-      </c>
-      <c r="F38" s="86" t="s">
-        <v>367</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>368</v>
-      </c>
-      <c r="H38" s="50" t="s">
-        <v>369</v>
-      </c>
-      <c r="I38" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="J38" s="50" t="s">
-        <v>371</v>
-      </c>
-      <c r="K38" s="50" t="s">
-        <v>372</v>
-      </c>
-      <c r="L38" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="M38" s="113" t="s">
-        <v>374</v>
-      </c>
-      <c r="N38" s="60" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="45">
-      <c r="A39" s="35" t="s">
-        <v>362</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>363</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E39" s="82" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F39" s="82" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L39" s="55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" spans="1:14" ht="30">
+    <row r="40" spans="1:14" ht="28.9">
       <c r="A40" s="35" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D40" s="44" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E40" s="87" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F40" s="87" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L40" s="55" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M40" s="43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N40" s="64" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="60">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="43.15">
       <c r="A41" s="37" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E41" s="88" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F41" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K41" s="26" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L41" s="59" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M41" s="11"/>
       <c r="N41" s="11"/>
     </row>
-    <row r="42" spans="1:14" ht="90">
+    <row r="42" spans="1:14" ht="72">
       <c r="A42" s="34" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D42" s="67" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E42" s="95" t="s">
+        <v>403</v>
+      </c>
+      <c r="F42" s="107" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="I42" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="F42" s="108" t="s">
-        <v>68</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>399</v>
-      </c>
       <c r="J42" s="19" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L42" s="60" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M42" s="60"/>
       <c r="N42" s="60"/>
     </row>
-    <row r="43" spans="1:14" ht="45">
+    <row r="43" spans="1:14" ht="43.15">
       <c r="A43" s="35" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E43" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F43" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K43" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L43" s="55" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M43" s="11"/>
       <c r="N43" s="11"/>
     </row>
     <row r="44" spans="1:14" ht="23.25" customHeight="1">
       <c r="A44" s="35" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D44" s="44" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E44" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F44" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L44" s="55" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M44" s="11"/>
       <c r="N44" s="11"/>
     </row>
-    <row r="45" spans="1:14" ht="30">
+    <row r="45" spans="1:14" ht="28.9">
       <c r="A45" s="35" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E45" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F45" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K45" s="14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L45" s="55" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M45" s="11"/>
       <c r="N45" s="11"/>
     </row>
     <row r="46" spans="1:14" ht="56.25" customHeight="1">
       <c r="A46" s="37" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E46" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="F46" s="96" t="s">
-        <v>429</v>
+        <v>114</v>
+      </c>
+      <c r="F46" s="116" t="s">
+        <v>431</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K46" s="26" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L46" s="59" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M46" s="43" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N46" s="64" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="31.5">
-      <c r="A47" s="97" t="s">
-        <v>397</v>
-      </c>
-      <c r="B47" s="98" t="s">
-        <v>398</v>
-      </c>
-      <c r="C47" s="98" t="s">
-        <v>436</v>
-      </c>
-      <c r="D47" s="99" t="s">
         <v>437</v>
       </c>
+    </row>
+    <row r="47" spans="1:14" ht="31.15">
+      <c r="A47" s="96" t="s">
+        <v>399</v>
+      </c>
+      <c r="B47" s="97" t="s">
+        <v>400</v>
+      </c>
+      <c r="C47" s="97" t="s">
+        <v>438</v>
+      </c>
+      <c r="D47" s="98" t="s">
+        <v>439</v>
+      </c>
       <c r="E47" s="85" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H47" s="74" t="s">
-        <v>440</v>
-      </c>
-      <c r="I47" s="97" t="s">
-        <v>441</v>
+        <v>442</v>
+      </c>
+      <c r="I47" s="96" t="s">
+        <v>443</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L47" s="55" t="s">
-        <v>444</v>
-      </c>
-      <c r="M47" s="100" t="s">
-        <v>445</v>
+        <v>446</v>
+      </c>
+      <c r="M47" s="99" t="s">
+        <v>447</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="145.5" customHeight="1">
-      <c r="A48" s="97" t="s">
-        <v>397</v>
-      </c>
-      <c r="B48" s="98" t="s">
-        <v>398</v>
-      </c>
-      <c r="C48" s="98" t="s">
-        <v>447</v>
-      </c>
-      <c r="D48" s="99" t="s">
-        <v>448</v>
+      <c r="A48" s="96" t="s">
+        <v>399</v>
+      </c>
+      <c r="B48" s="97" t="s">
+        <v>400</v>
+      </c>
+      <c r="C48" s="97" t="s">
+        <v>449</v>
+      </c>
+      <c r="D48" s="98" t="s">
+        <v>450</v>
       </c>
       <c r="E48" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H48" s="74" t="s">
-        <v>450</v>
-      </c>
-      <c r="I48" s="97" t="s">
-        <v>451</v>
+        <v>452</v>
+      </c>
+      <c r="I48" s="96" t="s">
+        <v>453</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L48" s="55" t="s">
-        <v>347</v>
-      </c>
-      <c r="M48" s="100" t="s">
-        <v>341</v>
+        <v>349</v>
+      </c>
+      <c r="M48" s="99" t="s">
+        <v>343</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="30">
-      <c r="A49" s="97" t="s">
-        <v>397</v>
-      </c>
-      <c r="B49" s="98" t="s">
-        <v>398</v>
-      </c>
-      <c r="C49" s="98" t="s">
-        <v>454</v>
-      </c>
-      <c r="D49" s="99" t="s">
-        <v>455</v>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="28.9">
+      <c r="A49" s="96" t="s">
+        <v>399</v>
+      </c>
+      <c r="B49" s="97" t="s">
+        <v>400</v>
+      </c>
+      <c r="C49" s="97" t="s">
+        <v>456</v>
+      </c>
+      <c r="D49" s="98" t="s">
+        <v>457</v>
       </c>
       <c r="E49" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F49" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H49" s="74" t="s">
+        <v>459</v>
+      </c>
+      <c r="I49" s="96" t="s">
         <v>456</v>
       </c>
-      <c r="G49" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H49" s="74" t="s">
-        <v>457</v>
-      </c>
-      <c r="I49" s="97" t="s">
-        <v>454</v>
-      </c>
       <c r="J49" s="14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L49" s="55" t="s">
-        <v>460</v>
-      </c>
-      <c r="M49" s="100" t="s">
-        <v>461</v>
+        <v>462</v>
+      </c>
+      <c r="M49" s="99" t="s">
+        <v>463</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="30">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="28.9">
       <c r="A50" s="39" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D50" s="52" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E50" s="91" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F50" s="91" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L50" s="56" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M50" s="56"/>
       <c r="N50" s="56"/>
     </row>
-    <row r="51" spans="1:14" ht="60">
+    <row r="51" spans="1:14" ht="43.15">
       <c r="A51" s="40" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D51" s="44" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E51" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F51" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H51" s="28" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I51" s="28" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J51" s="28" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L51" s="54" t="s">
         <v>2</v>
@@ -8381,2548 +8390,2548 @@
       <c r="M51" s="11"/>
       <c r="N51" s="11"/>
     </row>
-    <row r="52" spans="1:14" ht="30">
+    <row r="52" spans="1:14" ht="28.9">
       <c r="A52" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E52" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F52" s="82" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L52" s="55" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M52" s="11"/>
       <c r="N52" s="11"/>
     </row>
-    <row r="53" spans="1:14" ht="30">
+    <row r="53" spans="1:14" ht="28.9">
       <c r="A53" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E53" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="F53" s="96" t="s">
-        <v>429</v>
+        <v>114</v>
+      </c>
+      <c r="F53" s="116" t="s">
+        <v>431</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L53" s="55" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M53" s="43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N53" s="64" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="30">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="28.9">
       <c r="A54" s="37" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E54" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F54" s="82" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I54" s="26" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J54" s="26" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K54" s="26" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L54" s="59" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M54" s="43" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N54" s="64" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="75">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="57.6">
       <c r="A55" s="39" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D55" s="52" t="s">
+        <v>500</v>
+      </c>
+      <c r="E55" s="91" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" s="91" t="s">
+        <v>501</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="L55" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="M55" s="113" t="s">
+        <v>500</v>
+      </c>
+      <c r="N55" s="56" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="43.15">
+      <c r="A56" s="38" t="s">
+        <v>465</v>
+      </c>
+      <c r="B56" s="18" t="s">
         <v>498</v>
       </c>
-      <c r="E55" s="91" t="s">
-        <v>112</v>
-      </c>
-      <c r="F55" s="91" t="s">
-        <v>499</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>500</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>501</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>502</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="K55" s="13" t="s">
-        <v>504</v>
-      </c>
-      <c r="L55" s="56" t="s">
-        <v>505</v>
-      </c>
-      <c r="M55" s="114" t="s">
-        <v>498</v>
-      </c>
-      <c r="N55" s="56" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="45">
-      <c r="A56" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>496</v>
-      </c>
       <c r="C56" s="18" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E56" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F56" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H56" s="29" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I56" s="29" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J56" s="29" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K56" s="29" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L56" s="58" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>
     </row>
-    <row r="57" spans="1:14" ht="45">
+    <row r="57" spans="1:14" ht="28.9">
       <c r="A57" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E57" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F57" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H57" s="14" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L57" s="55" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M57" s="11"/>
       <c r="N57" s="11"/>
     </row>
-    <row r="58" spans="1:14" ht="30">
+    <row r="58" spans="1:14" ht="28.9">
       <c r="A58" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D58" s="44" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E58" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F58" s="87" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L58" s="55" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
     </row>
-    <row r="59" spans="1:14" ht="45">
+    <row r="59" spans="1:14" ht="31.15">
       <c r="A59" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E59" s="87" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F59" s="84" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H59" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L59" s="55" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M59" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N59" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="30">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="28.9">
       <c r="A60" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D60" s="11"/>
       <c r="E60" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F60" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L60" s="55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
     </row>
-    <row r="61" spans="1:14" ht="30">
+    <row r="61" spans="1:14" ht="28.9">
       <c r="A61" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D61" s="44" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E61" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F61" s="87" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L61" s="55" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M61" s="43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N61" s="64" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="30">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="28.9">
       <c r="A62" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D62" s="11"/>
       <c r="E62" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F62" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L62" s="55" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M62" s="11"/>
       <c r="N62" s="11"/>
     </row>
-    <row r="63" spans="1:14" ht="30">
+    <row r="63" spans="1:14" ht="28.9">
       <c r="A63" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D63" s="44" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E63" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F63" s="82" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K63" s="14" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L63" s="55" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
     </row>
-    <row r="64" spans="1:14" ht="45">
+    <row r="64" spans="1:14" ht="31.15">
       <c r="A64" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E64" s="82" t="s">
+        <v>563</v>
+      </c>
+      <c r="F64" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>565</v>
+      </c>
+      <c r="I64" s="14" t="s">
         <v>561</v>
       </c>
-      <c r="F64" s="92" t="s">
-        <v>68</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="H64" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="I64" s="14" t="s">
-        <v>559</v>
-      </c>
       <c r="J64" s="14" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L64" s="55" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M64" s="11"/>
       <c r="N64" s="11"/>
     </row>
-    <row r="65" spans="1:14" ht="45">
+    <row r="65" spans="1:14" ht="31.15">
       <c r="A65" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E65" s="82" t="s">
+        <v>571</v>
+      </c>
+      <c r="F65" s="92" t="s">
+        <v>70</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="I65" s="14" t="s">
         <v>569</v>
       </c>
-      <c r="F65" s="92" t="s">
-        <v>68</v>
-      </c>
-      <c r="G65" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>570</v>
-      </c>
-      <c r="I65" s="14" t="s">
-        <v>567</v>
-      </c>
       <c r="J65" s="14" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L65" s="55" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M65" s="11"/>
       <c r="N65" s="11"/>
     </row>
-    <row r="66" spans="1:14" ht="45">
+    <row r="66" spans="1:14" ht="43.15">
       <c r="A66" s="37" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C66" s="25" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D66" s="68" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E66" s="92" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F66" s="92" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I66" s="26" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="K66" s="26" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="L66" s="59" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M66" s="11"/>
       <c r="N66" s="11"/>
     </row>
-    <row r="67" spans="1:14" ht="45">
+    <row r="67" spans="1:14" ht="43.15">
       <c r="A67" s="39" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D67" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="E67" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" s="83" t="s">
+        <v>587</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="J67" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="K67" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="L67" s="56" t="s">
+        <v>592</v>
+      </c>
+      <c r="M67" s="56" t="s">
+        <v>586</v>
+      </c>
+      <c r="N67" s="56" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="43.15">
+      <c r="A68" s="38" t="s">
+        <v>465</v>
+      </c>
+      <c r="B68" s="18" t="s">
         <v>584</v>
       </c>
-      <c r="E67" s="83" t="s">
-        <v>112</v>
-      </c>
-      <c r="F67" s="83" t="s">
-        <v>585</v>
-      </c>
-      <c r="G67" s="12" t="s">
-        <v>500</v>
-      </c>
-      <c r="H67" s="13" t="s">
-        <v>586</v>
-      </c>
-      <c r="I67" s="13" t="s">
-        <v>587</v>
-      </c>
-      <c r="J67" s="13" t="s">
-        <v>588</v>
-      </c>
-      <c r="K67" s="13" t="s">
-        <v>589</v>
-      </c>
-      <c r="L67" s="56" t="s">
-        <v>590</v>
-      </c>
-      <c r="M67" s="56" t="s">
-        <v>584</v>
-      </c>
-      <c r="N67" s="56" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="45">
-      <c r="A68" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>582</v>
-      </c>
       <c r="C68" s="18" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E68" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F68" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H68" s="29" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J68" s="29" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K68" s="29" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L68" s="58" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M68" s="11"/>
       <c r="N68" s="11"/>
     </row>
-    <row r="69" spans="1:14" ht="45">
+    <row r="69" spans="1:14" ht="28.9">
       <c r="A69" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E69" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F69" s="85" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H69" s="14" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K69" s="14" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L69" s="55" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M69" s="11"/>
       <c r="N69" s="11"/>
     </row>
-    <row r="70" spans="1:14" ht="31.5">
+    <row r="70" spans="1:14" ht="31.15">
       <c r="A70" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E70" s="82" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F70" s="82" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L70" s="55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
     </row>
-    <row r="71" spans="1:14" ht="30">
+    <row r="71" spans="1:14" ht="28.9">
       <c r="A71" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E71" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F71" s="87" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H71" s="14" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K71" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L71" s="55" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M71" s="43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N71" s="64" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="31.5">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="31.15">
       <c r="A72" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D72" s="44" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E72" s="87" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F72" s="87" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G72" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>616</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="L72" s="55" t="s">
+        <v>529</v>
+      </c>
+      <c r="M72" s="43" t="s">
         <v>522</v>
       </c>
-      <c r="H72" s="14" t="s">
-        <v>613</v>
-      </c>
-      <c r="I72" s="14" t="s">
-        <v>614</v>
-      </c>
-      <c r="J72" s="14" t="s">
-        <v>615</v>
-      </c>
-      <c r="K72" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="L72" s="55" t="s">
-        <v>527</v>
-      </c>
-      <c r="M72" s="43" t="s">
-        <v>520</v>
-      </c>
       <c r="N72" s="64" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="30">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="28.9">
       <c r="A73" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D73" s="44" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F73" s="82" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H73" s="14" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K73" s="14" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L73" s="55" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M73" s="43" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N73" s="64" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="30">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="28.9">
       <c r="A74" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E74" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F74" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="I74" s="14" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="K74" s="14" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L74" s="55" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M74" s="11"/>
       <c r="N74" s="11"/>
     </row>
-    <row r="75" spans="1:14" ht="45">
+    <row r="75" spans="1:14" ht="28.9">
       <c r="A75" s="35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F75" s="82" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H75" s="14" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K75" s="14" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="L75" s="55" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M75" s="43" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N75" s="64" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="30">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="28.9">
       <c r="A76" s="36" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D76" s="68" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E76" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F76" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H76" s="23" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K76" s="23" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L76" s="57" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M76" s="43" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N76" s="64" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="45">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="43.15">
       <c r="A77" s="16" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D77" s="67" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E77" s="89" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F77" s="89" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J77" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="K77" s="19" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L77" s="60" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M77" s="60"/>
       <c r="N77" s="60"/>
     </row>
-    <row r="78" spans="1:14" ht="30">
+    <row r="78" spans="1:14" ht="28.9">
       <c r="A78" s="20" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E78" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F78" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H78" s="14" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K78" s="14" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L78" s="55" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M78" s="11"/>
       <c r="N78" s="11"/>
     </row>
-    <row r="79" spans="1:14" ht="30">
+    <row r="79" spans="1:14" ht="28.9">
       <c r="A79" s="20" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D79" s="43" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E79" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F79" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H79" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="I79" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="I79" s="14" t="s">
-        <v>662</v>
-      </c>
       <c r="J79" s="14" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="K79" s="14" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L79" s="55" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M79" s="11"/>
       <c r="N79" s="11"/>
     </row>
-    <row r="80" spans="1:14" ht="45">
+    <row r="80" spans="1:14" ht="43.15">
       <c r="A80" s="20" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D80" s="43" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E80" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F80" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="K80" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L80" s="55" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M80" s="11"/>
       <c r="N80" s="11"/>
     </row>
-    <row r="81" spans="1:14" ht="30">
+    <row r="81" spans="1:14" ht="28.9">
       <c r="A81" s="20" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D81" s="43" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E81" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F81" s="93" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H81" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="I81" s="14" t="s">
         <v>675</v>
       </c>
-      <c r="I81" s="14" t="s">
-        <v>673</v>
-      </c>
       <c r="J81" s="14" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="K81" s="14" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L81" s="55" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M81" s="43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N81" s="64" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="31.5">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="31.15">
       <c r="A82" s="20" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D82" s="43" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E82" s="90" t="s">
-        <v>680</v>
-      </c>
-      <c r="F82" s="116" t="s">
-        <v>681</v>
+        <v>682</v>
+      </c>
+      <c r="F82" s="115" t="s">
+        <v>683</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="K82" s="14" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="L82" s="55" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M82" s="43" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N82" s="64" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="45">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="43.15">
       <c r="A83" s="20" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D83" s="43" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E83" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F83" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H83" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="I83" s="14" t="s">
         <v>688</v>
       </c>
-      <c r="I83" s="14" t="s">
-        <v>686</v>
-      </c>
       <c r="J83" s="14" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="K83" s="14" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="L83" s="55" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M83" s="11"/>
       <c r="N83" s="11"/>
     </row>
-    <row r="84" spans="1:14" ht="45">
+    <row r="84" spans="1:14" ht="43.15">
       <c r="A84" s="20" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D84" s="43" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E84" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F84" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H84" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="I84" s="14" t="s">
         <v>693</v>
       </c>
-      <c r="I84" s="14" t="s">
-        <v>691</v>
-      </c>
       <c r="J84" s="14" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K84" s="14" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="L84" s="55" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M84" s="11"/>
       <c r="N84" s="11"/>
     </row>
-    <row r="85" spans="1:14" ht="30">
+    <row r="85" spans="1:14" ht="28.9">
       <c r="A85" s="11" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D85" s="43" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E85" s="90" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F85" s="90" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H85" s="14" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="K85" s="14" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="L85" s="55" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M85" s="11"/>
       <c r="N85" s="11"/>
     </row>
-    <row r="86" spans="1:14" ht="45">
+    <row r="86" spans="1:14" ht="43.15">
       <c r="A86" s="11" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E86" s="90" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F86" s="90" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H86" s="14" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="K86" s="14" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="L86" s="55" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="M86" s="43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N86" s="64" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="30">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" ht="28.9">
       <c r="A87" s="49"/>
       <c r="B87" s="45" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C87" s="45" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E87" s="86" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F87" s="86" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G87" s="45" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="H87" s="50" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I87" s="50" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="J87" s="50" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="K87" s="50" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="L87" s="61" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="M87" s="61"/>
       <c r="N87" s="61"/>
     </row>
-    <row r="88" spans="1:14" ht="45">
+    <row r="88" spans="1:14" ht="43.15">
       <c r="A88" s="20"/>
       <c r="B88" s="11" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E88" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F88" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G88" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="I88" s="14" t="s">
         <v>720</v>
       </c>
-      <c r="H88" s="14" t="s">
-        <v>721</v>
-      </c>
-      <c r="I88" s="14" t="s">
-        <v>718</v>
-      </c>
       <c r="J88" s="14" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="K88" s="14" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="L88" s="55" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M88" s="11"/>
       <c r="N88" s="11"/>
     </row>
-    <row r="89" spans="1:14" ht="60">
+    <row r="89" spans="1:14" ht="43.15">
       <c r="A89" s="20"/>
       <c r="B89" s="11" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E89" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F89" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H89" s="14" t="s">
+        <v>729</v>
+      </c>
+      <c r="I89" s="14" t="s">
         <v>727</v>
       </c>
-      <c r="I89" s="14" t="s">
-        <v>725</v>
-      </c>
       <c r="J89" s="14" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="L89" s="55" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="M89" s="11"/>
       <c r="N89" s="11"/>
     </row>
-    <row r="90" spans="1:14" ht="30">
+    <row r="90" spans="1:14" ht="28.9">
       <c r="A90" s="21"/>
       <c r="B90" s="22" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E90" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F90" s="82" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H90" s="23" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="I90" s="23" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="J90" s="23" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="K90" s="23" t="s">
+        <v>737</v>
+      </c>
+      <c r="L90" s="57" t="s">
         <v>735</v>
-      </c>
-      <c r="L90" s="57" t="s">
-        <v>733</v>
       </c>
       <c r="M90" s="11"/>
       <c r="N90" s="11"/>
     </row>
-    <row r="91" spans="1:14" ht="31.5">
+    <row r="91" spans="1:14" ht="31.15">
       <c r="A91" s="16" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C91" s="17" t="s">
+        <v>740</v>
+      </c>
+      <c r="D91" s="67" t="s">
+        <v>741</v>
+      </c>
+      <c r="E91" s="89" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" s="89" t="s">
+        <v>742</v>
+      </c>
+      <c r="G91" s="45" t="s">
         <v>738</v>
       </c>
-      <c r="D91" s="67" t="s">
-        <v>739</v>
-      </c>
-      <c r="E91" s="89" t="s">
-        <v>112</v>
-      </c>
-      <c r="F91" s="89" t="s">
-        <v>740</v>
-      </c>
-      <c r="G91" s="45" t="s">
-        <v>736</v>
-      </c>
       <c r="H91" s="17" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="K91" s="17" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="L91" s="62" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="M91" s="62"/>
       <c r="N91" s="62"/>
     </row>
-    <row r="92" spans="1:14" ht="45">
+    <row r="92" spans="1:14" ht="43.15">
       <c r="A92" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D92" s="42" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E92" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F92" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H92" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="I92" s="14" t="s">
         <v>748</v>
       </c>
-      <c r="I92" s="14" t="s">
-        <v>746</v>
-      </c>
       <c r="J92" s="14" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="K92" s="14" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="L92" s="55" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
     </row>
-    <row r="93" spans="1:14" ht="45">
+    <row r="93" spans="1:14" ht="28.9">
       <c r="A93" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D93" s="43" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E93" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F93" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H93" s="14" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="L93" s="55" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="M93" s="11"/>
       <c r="N93" s="11"/>
     </row>
-    <row r="94" spans="1:14" ht="30">
+    <row r="94" spans="1:14" ht="28.9">
       <c r="A94" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D94" s="44" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E94" s="87" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F94" s="87" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H94" s="14" t="s">
+        <v>762</v>
+      </c>
+      <c r="I94" s="14" t="s">
         <v>760</v>
       </c>
-      <c r="I94" s="14" t="s">
-        <v>758</v>
-      </c>
       <c r="J94" s="14" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="K94" s="14" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="L94" s="55" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M94" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N94" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" ht="60">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="43.15">
       <c r="A95" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D95" s="43" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E95" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F95" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H95" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="I95" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="I95" s="14" t="s">
-        <v>763</v>
-      </c>
       <c r="J95" s="14" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="L95" s="55" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M95" s="11"/>
       <c r="N95" s="11"/>
     </row>
-    <row r="96" spans="1:14" ht="45">
+    <row r="96" spans="1:14" ht="43.15">
       <c r="A96" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D96" s="43" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E96" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F96" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H96" s="14" t="s">
+        <v>772</v>
+      </c>
+      <c r="I96" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="I96" s="14" t="s">
-        <v>768</v>
-      </c>
       <c r="J96" s="14" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="K96" s="14" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="L96" s="55" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="M96" s="11"/>
       <c r="N96" s="11"/>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" ht="15.6">
       <c r="A97" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D97" s="43" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E97" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F97" s="90" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H97" s="14" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="J97" s="14" t="s">
+        <v>781</v>
+      </c>
+      <c r="K97" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="L97" s="55" t="s">
+        <v>783</v>
+      </c>
+      <c r="M97" s="43" t="s">
+        <v>784</v>
+      </c>
+      <c r="N97" s="64" t="s">
         <v>779</v>
       </c>
-      <c r="K97" s="14" t="s">
-        <v>780</v>
-      </c>
-      <c r="L97" s="55" t="s">
-        <v>781</v>
-      </c>
-      <c r="M97" s="43" t="s">
-        <v>782</v>
-      </c>
-      <c r="N97" s="64" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="47.25">
+    </row>
+    <row r="98" spans="1:14" ht="31.15">
       <c r="A98" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D98" s="44" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E98" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F98" s="87" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H98" s="14" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="K98" s="14" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="L98" s="55" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="M98" s="11"/>
       <c r="N98" s="11"/>
     </row>
-    <row r="99" spans="1:14" ht="45">
+    <row r="99" spans="1:14" ht="43.15">
       <c r="A99" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D99" s="43" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="E99" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F99" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H99" s="14" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="K99" s="14" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="L99" s="55" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="M99" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N99" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="30">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="28.9">
       <c r="A100" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D100" s="43" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E100" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F100" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H100" s="14" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="K100" s="14" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L100" s="55" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="M100" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N100" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" ht="47.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="31.15">
       <c r="A101" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D101" s="43" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E101" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F101" s="87" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H101" s="14" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="I101" s="14" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="K101" s="14" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="L101" s="55" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="M101" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N101" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" ht="45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="28.9">
       <c r="A102" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="D102" s="43" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E102" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F102" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H102" s="14" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="K102" s="14" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="L102" s="55" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M102" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N102" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" ht="45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="43.15">
       <c r="A103" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D103" s="43" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E103" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F103" s="90" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H103" s="14" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="I103" s="14" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="K103" s="14" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="L103" s="55" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="M103" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N103" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" ht="45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="43.15">
       <c r="A104" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D104" s="43" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E104" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F104" s="90" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H104" s="14" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="I104" s="14" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="K104" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="L104" s="55" t="s">
         <v>833</v>
       </c>
-      <c r="L104" s="55" t="s">
-        <v>831</v>
-      </c>
       <c r="M104" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N104" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" ht="90">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="72">
       <c r="A105" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E105" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F105" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H105" s="14" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="I105" s="14" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K105" s="14" t="s">
+        <v>840</v>
+      </c>
+      <c r="L105" s="55" t="s">
         <v>838</v>
       </c>
-      <c r="L105" s="55" t="s">
-        <v>836</v>
-      </c>
       <c r="M105" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N105" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" ht="30">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="28.9">
       <c r="A106" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D106" s="43" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E106" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F106" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H106" s="14" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="I106" s="14" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="K106" s="14" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="L106" s="55" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="M106" s="11"/>
       <c r="N106" s="11"/>
     </row>
-    <row r="107" spans="1:14" ht="30">
+    <row r="107" spans="1:14" ht="28.9">
       <c r="A107" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D107" s="43" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E107" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F107" s="90" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H107" s="14" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="I107" s="14" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="K107" s="14" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="L107" s="55" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="M107" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N107" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" ht="45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="43.15">
       <c r="A108" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D108" s="43" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="E108" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F108" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G108" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H108" s="14" t="s">
+        <v>858</v>
+      </c>
+      <c r="I108" s="14" t="s">
         <v>856</v>
       </c>
-      <c r="I108" s="14" t="s">
-        <v>854</v>
-      </c>
       <c r="J108" s="14" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="K108" s="14" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="L108" s="55" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="M108" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N108" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" ht="30">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="28.9">
       <c r="A109" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D109" s="43" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E109" s="82" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F109" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H109" s="14" t="s">
+        <v>864</v>
+      </c>
+      <c r="I109" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="I109" s="14" t="s">
-        <v>860</v>
-      </c>
       <c r="J109" s="14" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="K109" s="14" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="L109" s="55" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="M109" s="41" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="N109" s="64" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" ht="60">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="43.15">
       <c r="A110" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E110" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F110" s="82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H110" s="14" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="I110" s="14" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="K110" s="14" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="L110" s="55" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="M110" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N110" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" ht="75">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="72">
       <c r="A111" s="35" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D111" s="43" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E111" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F111" s="90" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H111" s="14" t="s">
+        <v>876</v>
+      </c>
+      <c r="I111" s="14" t="s">
         <v>874</v>
       </c>
-      <c r="I111" s="14" t="s">
-        <v>872</v>
-      </c>
       <c r="J111" s="14" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="K111" s="14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="L111" s="55" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="M111" s="43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N111" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" ht="31.5">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" ht="31.15">
       <c r="A112" s="36" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C112" s="23" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D112" s="66" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E112" s="94" t="s">
+        <v>882</v>
+      </c>
+      <c r="F112" s="94" t="s">
+        <v>882</v>
+      </c>
+      <c r="G112" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112" s="23" t="s">
+        <v>883</v>
+      </c>
+      <c r="I112" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="F112" s="94" t="s">
-        <v>880</v>
-      </c>
-      <c r="G112" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H112" s="23" t="s">
-        <v>881</v>
-      </c>
-      <c r="I112" s="23" t="s">
-        <v>878</v>
-      </c>
       <c r="J112" s="23" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="L112" s="57" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="M112" s="43" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="N112" s="64" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
   </sheetData>
@@ -11041,6 +11050,7 @@
     <hyperlink ref="D109" r:id="rId112" xr:uid="{6420CBC4-2133-4E71-B3DF-6BC79509B246}"/>
     <hyperlink ref="M109" r:id="rId113" display="https://ncithesaurus.nci.nih.gov/ncitbrowser/ConceptReport.jsp?dictionary=NCI_Thesaurus&amp;ns=ncit&amp;code=C66767" xr:uid="{42FE7547-B685-4EC2-B8F8-D5BDD3D01B60}"/>
     <hyperlink ref="F82" r:id="rId114" xr:uid="{7AECE34F-859F-4D3F-9267-FF628E946656}"/>
+    <hyperlink ref="D2" r:id="rId115" xr:uid="{B34030A7-20B1-480D-AC20-DDEC2904F812}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11052,7 +11062,7 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
     <col min="2" max="2" width="28.42578125" customWidth="1"/>
@@ -11060,339 +11070,332 @@
     <col min="4" max="4" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1">
+    <row r="1" spans="1:4" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="45">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.15">
       <c r="A2" s="129" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D2" s="132" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" thickBot="1">
       <c r="A3" s="130"/>
       <c r="B3" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>893</v>
-      </c>
-      <c r="D3" s="134"/>
-    </row>
-    <row r="4" spans="1:4" ht="30">
+        <v>895</v>
+      </c>
+      <c r="D3" s="133"/>
+    </row>
+    <row r="4" spans="1:4" ht="28.9">
       <c r="A4" s="130"/>
       <c r="B4" s="6" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>895</v>
-      </c>
-      <c r="D4" s="135" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30.75" thickBot="1">
+        <v>897</v>
+      </c>
+      <c r="D4" s="134" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29.45" thickBot="1">
       <c r="A5" s="130"/>
       <c r="B5" s="7" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>898</v>
-      </c>
-      <c r="D5" s="137"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1">
+        <v>900</v>
+      </c>
+      <c r="D5" s="135"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" thickBot="1">
       <c r="A6" s="131"/>
       <c r="B6" s="5" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="5" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30.75" thickBot="1">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29.45" thickBot="1">
       <c r="A7" s="129" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30.75" thickBot="1">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29.45" thickBot="1">
       <c r="A8" s="131"/>
       <c r="B8" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="30">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="129" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="C9" s="135" t="s">
-        <v>907</v>
-      </c>
-      <c r="D9" s="135" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30">
+        <v>720</v>
+      </c>
+      <c r="C9" s="134" t="s">
+        <v>909</v>
+      </c>
+      <c r="D9" s="134" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="130"/>
       <c r="B10" s="6" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C10" s="136"/>
       <c r="D10" s="136"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" thickBot="1">
+    <row r="11" spans="1:4" ht="15" thickBot="1">
       <c r="A11" s="131"/>
       <c r="B11" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+    </row>
+    <row r="12" spans="1:4" ht="28.9">
+      <c r="A12" s="129" t="s">
+        <v>747</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C12" s="132" t="s">
         <v>909</v>
       </c>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-    </row>
-    <row r="12" spans="1:4" ht="30">
-      <c r="A12" s="129" t="s">
-        <v>745</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="C12" s="132" t="s">
-        <v>907</v>
-      </c>
       <c r="D12" s="132" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="130"/>
       <c r="B13" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
+        <v>913</v>
+      </c>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="130"/>
       <c r="B14" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="C14" s="133"/>
-      <c r="D14" s="133"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" thickBot="1">
+        <v>914</v>
+      </c>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" thickBot="1">
       <c r="A15" s="130"/>
       <c r="B15" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="C15" s="134"/>
-      <c r="D15" s="134"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" thickBot="1">
+        <v>760</v>
+      </c>
+      <c r="C15" s="133"/>
+      <c r="D15" s="133"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" thickBot="1">
       <c r="A16" s="130"/>
       <c r="B16" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" thickBot="1">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickBot="1">
       <c r="A17" s="130"/>
       <c r="B17" s="5" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="5" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="130"/>
       <c r="B18" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="C18" s="135" t="s">
-        <v>907</v>
-      </c>
-      <c r="D18" s="135" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
+        <v>919</v>
+      </c>
+      <c r="C18" s="134" t="s">
+        <v>909</v>
+      </c>
+      <c r="D18" s="134" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.6">
       <c r="A19" s="130"/>
       <c r="B19" s="9" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C19" s="136"/>
       <c r="D19" s="136"/>
     </row>
-    <row r="20" spans="1:4" ht="31.5">
+    <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="130"/>
       <c r="B20" s="9" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C20" s="136"/>
       <c r="D20" s="136"/>
     </row>
-    <row r="21" spans="1:4" ht="47.25">
+    <row r="21" spans="1:4" ht="46.9">
       <c r="A21" s="130"/>
       <c r="B21" s="9" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C21" s="136"/>
       <c r="D21" s="136"/>
     </row>
-    <row r="22" spans="1:4" ht="47.25">
+    <row r="22" spans="1:4" ht="46.9">
       <c r="A22" s="130"/>
       <c r="B22" s="9" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C22" s="136"/>
       <c r="D22" s="136"/>
     </row>
-    <row r="23" spans="1:4" ht="47.25">
+    <row r="23" spans="1:4" ht="46.9">
       <c r="A23" s="130"/>
       <c r="B23" s="9" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C23" s="136"/>
       <c r="D23" s="136"/>
     </row>
-    <row r="24" spans="1:4" ht="47.25">
+    <row r="24" spans="1:4" ht="46.9">
       <c r="A24" s="130"/>
       <c r="B24" s="9" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C24" s="136"/>
       <c r="D24" s="136"/>
     </row>
-    <row r="25" spans="1:4" ht="16.5" thickBot="1">
+    <row r="25" spans="1:4" ht="16.149999999999999" thickBot="1">
       <c r="A25" s="130"/>
       <c r="B25" s="10" t="s">
-        <v>925</v>
-      </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
+        <v>927</v>
+      </c>
+      <c r="C25" s="135"/>
+      <c r="D25" s="135"/>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="130"/>
       <c r="B26" s="132" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C26" s="132" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" thickBot="1">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" thickBot="1">
       <c r="A27" s="130"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="134"/>
+      <c r="B27" s="133"/>
+      <c r="C27" s="133"/>
       <c r="D27" s="5" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="130"/>
       <c r="B28" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="C28" s="135" t="s">
-        <v>907</v>
-      </c>
-      <c r="D28" s="135" t="s">
-        <v>929</v>
+        <v>869</v>
+      </c>
+      <c r="C28" s="134" t="s">
+        <v>909</v>
+      </c>
+      <c r="D28" s="134" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="130"/>
       <c r="B29" s="6" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C29" s="136"/>
       <c r="D29" s="136"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" thickBot="1">
+    <row r="30" spans="1:4" ht="15" thickBot="1">
       <c r="A30" s="130"/>
       <c r="B30" s="7" t="s">
-        <v>878</v>
-      </c>
-      <c r="C30" s="137"/>
-      <c r="D30" s="137"/>
+        <v>880</v>
+      </c>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="131"/>
       <c r="B31" s="5" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="5" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A32" s="109" t="s">
-        <v>463</v>
-      </c>
-      <c r="B32" s="112" t="s">
-        <v>528</v>
+      <c r="A32" s="108" t="s">
+        <v>465</v>
+      </c>
+      <c r="B32" s="111" t="s">
+        <v>530</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="110" t="s">
-        <v>930</v>
+      <c r="D32" s="109" t="s">
+        <v>932</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
     <mergeCell ref="A12:A31"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="D12:D15"/>
@@ -11402,6 +11405,13 @@
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C30"/>
     <mergeCell ref="D28:D30"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D9:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11409,6 +11419,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" xsi:nil="true"/>
@@ -11419,18 +11438,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c43450b8c34e20acaf1756fc6612395">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2045bb9c165ab785731dcc392b30c8" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1e59347b0eab0f591b37435e30882b37">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="051b7680b3f8fbabaffc0bcf09c3613a" ns2:_="" ns3:_="">
     <xsd:import namespace="a46baf18-fe18-4a25-9dd7-6596c31699af"/>
     <xsd:import namespace="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b"/>
     <xsd:element name="properties">
@@ -11453,6 +11463,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -11520,6 +11531,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -11664,30 +11680,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F801566-3BBB-403B-A712-99CD7B76036B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a46baf18-fe18-4a25-9dd7-6596c31699af"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35E4C303-1772-4B4C-8C94-BC3876300815}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35E4C303-1772-4B4C-8C94-BC3876300815}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F801566-3BBB-403B-A712-99CD7B76036B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE3ACC3-1199-427F-B770-E81F861336EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ECFF57C-7483-46C1-A0D2-6E11A4606E92}"/>
 </file>